--- a/three_gate/reports/monthly_report.xlsx
+++ b/three_gate/reports/monthly_report.xlsx
@@ -59059,7 +59059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R198"/>
+  <dimension ref="A1:R207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -70082,59 +70082,63 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>原油 WTI</t>
+          <t>比特幣</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>102.01</v>
+        <v>78162.48</v>
       </c>
       <c r="E172" t="n">
-        <v>106.75</v>
+        <v>78242.55</v>
       </c>
       <c r="F172" t="n">
-        <v>101.21</v>
+        <v>74944.59</v>
       </c>
       <c r="G172" t="n">
-        <v>105.83</v>
+        <v>75612.50999999999</v>
       </c>
       <c r="H172" t="n">
-        <v>4.44</v>
+        <v>-2550.88</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0326</v>
       </c>
       <c r="J172" t="n">
-        <v>96.11</v>
+        <v>73165.8</v>
       </c>
       <c r="K172" t="n">
-        <v>96.3</v>
+        <v>75059.41</v>
       </c>
       <c r="L172" t="n">
-        <v>99.18000000000001</v>
+        <v>76562.59</v>
       </c>
       <c r="M172" t="n">
-        <v>102.06</v>
+        <v>78065.77</v>
       </c>
       <c r="N172" t="n">
-        <v>103.6</v>
+        <v>79764.17</v>
       </c>
       <c r="O172" t="n">
-        <v>105.13</v>
+        <v>81462.57000000001</v>
       </c>
       <c r="P172" t="n">
-        <v>109.37</v>
+        <v>82770.53</v>
       </c>
       <c r="Q172" s="6" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="R172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -70144,63 +70148,59 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>原油 WTI</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>25360.32</v>
+        <v>102.01</v>
       </c>
       <c r="E173" t="n">
-        <v>25478.98</v>
+        <v>106.75</v>
       </c>
       <c r="F173" t="n">
-        <v>25172.89</v>
+        <v>101.21</v>
       </c>
       <c r="G173" t="n">
-        <v>25402.28</v>
+        <v>105.83</v>
       </c>
       <c r="H173" t="n">
-        <v>-38.53</v>
+        <v>4.44</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0438</v>
       </c>
       <c r="J173" t="n">
-        <v>25102.26</v>
+        <v>96.11</v>
       </c>
       <c r="K173" t="n">
-        <v>25219.38</v>
+        <v>96.3</v>
       </c>
       <c r="L173" t="n">
-        <v>25329.18</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="M173" t="n">
-        <v>25438.98</v>
+        <v>102.06</v>
       </c>
       <c r="N173" t="n">
-        <v>25552.44</v>
+        <v>103.6</v>
       </c>
       <c r="O173" t="n">
-        <v>25665.9</v>
+        <v>105.13</v>
       </c>
       <c r="P173" t="n">
-        <v>25772.04</v>
+        <v>109.37</v>
       </c>
       <c r="Q173" s="6" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -70210,59 +70210,63 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>S&amp;P 500 期貨</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>7631</v>
+        <v>25360.32</v>
       </c>
       <c r="E174" t="n">
-        <v>7633.25</v>
+        <v>25478.98</v>
       </c>
       <c r="F174" t="n">
-        <v>7576.75</v>
+        <v>25172.89</v>
       </c>
       <c r="G174" t="n">
-        <v>7589.25</v>
+        <v>25402.28</v>
       </c>
       <c r="H174" t="n">
-        <v>-35.75</v>
+        <v>-38.53</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0015</v>
       </c>
       <c r="J174" t="n">
-        <v>7535.5</v>
+        <v>25102.26</v>
       </c>
       <c r="K174" t="n">
-        <v>7567.81</v>
+        <v>25219.38</v>
       </c>
       <c r="L174" t="n">
-        <v>7595.88</v>
+        <v>25329.18</v>
       </c>
       <c r="M174" t="n">
-        <v>7623.94</v>
+        <v>25438.98</v>
       </c>
       <c r="N174" t="n">
-        <v>7654.12</v>
+        <v>25552.44</v>
       </c>
       <c r="O174" t="n">
-        <v>7684.31</v>
+        <v>25665.9</v>
       </c>
       <c r="P174" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="Q174" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
+        <v>25772.04</v>
+      </c>
+      <c r="Q174" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -70272,52 +70276,52 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FTSE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FTSE 100</t>
+          <t>S&amp;P 500 期貨</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10697.8</v>
+        <v>7631</v>
       </c>
       <c r="E175" t="n">
-        <v>10697.8</v>
+        <v>7633.25</v>
       </c>
       <c r="F175" t="n">
-        <v>10586.4</v>
+        <v>7576.75</v>
       </c>
       <c r="G175" t="n">
-        <v>10658.1</v>
+        <v>7589.25</v>
       </c>
       <c r="H175" t="n">
-        <v>-39.5</v>
+        <v>-35.75</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0047</v>
       </c>
       <c r="J175" t="n">
-        <v>10566.9</v>
+        <v>7535.5</v>
       </c>
       <c r="K175" t="n">
-        <v>10615.95</v>
+        <v>7567.81</v>
       </c>
       <c r="L175" t="n">
-        <v>10655.6</v>
+        <v>7595.88</v>
       </c>
       <c r="M175" t="n">
-        <v>10695.25</v>
+        <v>7623.94</v>
       </c>
       <c r="N175" t="n">
-        <v>10739.6</v>
+        <v>7654.12</v>
       </c>
       <c r="O175" t="n">
-        <v>10783.95</v>
+        <v>7684.31</v>
       </c>
       <c r="P175" t="n">
-        <v>10818.9</v>
+        <v>7710.25</v>
       </c>
       <c r="Q175" s="7" t="inlineStr">
         <is>
@@ -70334,63 +70338,59 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>黃金</t>
+          <t>以太幣</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4340.3</v>
+        <v>2514.36</v>
       </c>
       <c r="E176" t="n">
-        <v>4358.2</v>
+        <v>2519.32</v>
       </c>
       <c r="F176" t="n">
-        <v>4301.6</v>
+        <v>2357.96</v>
       </c>
       <c r="G176" t="n">
-        <v>4332.8</v>
+        <v>2399.09</v>
       </c>
       <c r="H176" t="n">
-        <v>-19.1</v>
+        <v>-115.32</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0459</v>
       </c>
       <c r="J176" t="n">
-        <v>4189.2</v>
+        <v>2318.45</v>
       </c>
       <c r="K176" t="n">
-        <v>4251.6</v>
+        <v>2355.18</v>
       </c>
       <c r="L176" t="n">
-        <v>4300</v>
+        <v>2440.92</v>
       </c>
       <c r="M176" t="n">
-        <v>4348.4</v>
+        <v>2526.66</v>
       </c>
       <c r="N176" t="n">
-        <v>4403.8</v>
+        <v>2587.9</v>
       </c>
       <c r="O176" t="n">
-        <v>4459.2</v>
+        <v>2649.13</v>
       </c>
       <c r="P176" t="n">
-        <v>4500.6</v>
+        <v>2759.38</v>
       </c>
       <c r="Q176" s="7" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -70400,63 +70400,59 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HSI</t>
+          <t>FTSE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>恆生指數</t>
+          <t>FTSE 100</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>24934.06</v>
+        <v>10697.8</v>
       </c>
       <c r="E177" t="n">
-        <v>24934.06</v>
+        <v>10697.8</v>
       </c>
       <c r="F177" t="n">
-        <v>24657.01</v>
+        <v>10586.4</v>
       </c>
       <c r="G177" t="n">
-        <v>24667.24</v>
+        <v>10658.1</v>
       </c>
       <c r="H177" t="n">
-        <v>-250.36</v>
+        <v>-39.5</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0037</v>
       </c>
       <c r="J177" t="n">
-        <v>24397.98</v>
+        <v>10566.9</v>
       </c>
       <c r="K177" t="n">
-        <v>24715.18</v>
+        <v>10615.95</v>
       </c>
       <c r="L177" t="n">
-        <v>24785.53</v>
+        <v>10655.6</v>
       </c>
       <c r="M177" t="n">
-        <v>24855.89</v>
+        <v>10695.25</v>
       </c>
       <c r="N177" t="n">
-        <v>25049.67</v>
+        <v>10739.6</v>
       </c>
       <c r="O177" t="n">
-        <v>25243.44</v>
+        <v>10783.95</v>
       </c>
       <c r="P177" t="n">
-        <v>25190.37</v>
+        <v>10818.9</v>
       </c>
       <c r="Q177" s="7" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -70466,52 +70462,52 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>N225</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>日經 225</t>
+          <t>黃金</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>63190.37</v>
+        <v>4340.3</v>
       </c>
       <c r="E178" t="n">
-        <v>64101</v>
+        <v>4358.2</v>
       </c>
       <c r="F178" t="n">
-        <v>63067.18</v>
+        <v>4301.6</v>
       </c>
       <c r="G178" t="n">
-        <v>63484.1</v>
+        <v>4332.8</v>
       </c>
       <c r="H178" t="n">
-        <v>-8.890000000000001</v>
+        <v>-19.1</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0044</v>
       </c>
       <c r="J178" t="n">
-        <v>61760.83</v>
+        <v>4189.2</v>
       </c>
       <c r="K178" t="n">
-        <v>62669.7</v>
+        <v>4251.6</v>
       </c>
       <c r="L178" t="n">
-        <v>63010.31</v>
+        <v>4300</v>
       </c>
       <c r="M178" t="n">
-        <v>63350.92</v>
+        <v>4348.4</v>
       </c>
       <c r="N178" t="n">
-        <v>63975.66</v>
+        <v>4403.8</v>
       </c>
       <c r="O178" t="n">
-        <v>64600.41</v>
+        <v>4459.2</v>
       </c>
       <c r="P178" t="n">
-        <v>64656.88</v>
+        <v>4500.6</v>
       </c>
       <c r="Q178" s="7" t="inlineStr">
         <is>
@@ -70520,7 +70516,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -70532,59 +70528,63 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>HSI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>天然氣</t>
+          <t>恆生指數</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2.88</v>
+        <v>24934.06</v>
       </c>
       <c r="E179" t="n">
-        <v>2.95</v>
+        <v>24934.06</v>
       </c>
       <c r="F179" t="n">
-        <v>2.87</v>
+        <v>24657.01</v>
       </c>
       <c r="G179" t="n">
-        <v>2.92</v>
+        <v>24667.24</v>
       </c>
       <c r="H179" t="n">
-        <v>0.02</v>
+        <v>-250.36</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="J179" t="n">
-        <v>2.79</v>
+        <v>24397.98</v>
       </c>
       <c r="K179" t="n">
-        <v>2.84</v>
+        <v>24715.18</v>
       </c>
       <c r="L179" t="n">
-        <v>2.86</v>
+        <v>24785.53</v>
       </c>
       <c r="M179" t="n">
-        <v>2.89</v>
+        <v>24855.89</v>
       </c>
       <c r="N179" t="n">
-        <v>2.93</v>
+        <v>25049.67</v>
       </c>
       <c r="O179" t="n">
-        <v>2.97</v>
+        <v>25243.44</v>
       </c>
       <c r="P179" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q179" s="6" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr"/>
+        <v>25190.37</v>
+      </c>
+      <c r="Q179" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -70594,52 +70594,52 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>N225</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Nasdaq 100 期貨</t>
+          <t>日經 225</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>29200</v>
+        <v>63190.37</v>
       </c>
       <c r="E180" t="n">
-        <v>29200</v>
+        <v>64101</v>
       </c>
       <c r="F180" t="n">
-        <v>28918.75</v>
+        <v>63067.18</v>
       </c>
       <c r="G180" t="n">
-        <v>28955</v>
+        <v>63484.1</v>
       </c>
       <c r="H180" t="n">
-        <v>-197.25</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0001</v>
       </c>
       <c r="J180" t="n">
-        <v>28329.5</v>
+        <v>61760.83</v>
       </c>
       <c r="K180" t="n">
-        <v>28711.81</v>
+        <v>62669.7</v>
       </c>
       <c r="L180" t="n">
-        <v>28908.88</v>
+        <v>63010.31</v>
       </c>
       <c r="M180" t="n">
-        <v>29105.94</v>
+        <v>63350.92</v>
       </c>
       <c r="N180" t="n">
-        <v>29395.62</v>
+        <v>63975.66</v>
       </c>
       <c r="O180" t="n">
-        <v>29685.31</v>
+        <v>64600.41</v>
       </c>
       <c r="P180" t="n">
-        <v>29789.75</v>
+        <v>64656.88</v>
       </c>
       <c r="Q180" s="7" t="inlineStr">
         <is>
@@ -70648,7 +70648,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -70660,56 +70660,56 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Russell 2000 期貨</t>
+          <t>天然氣</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2896.4</v>
+        <v>2.88</v>
       </c>
       <c r="E181" t="n">
-        <v>2896.5</v>
+        <v>2.95</v>
       </c>
       <c r="F181" t="n">
-        <v>2862.7</v>
+        <v>2.87</v>
       </c>
       <c r="G181" t="n">
-        <v>2873.1</v>
+        <v>2.92</v>
       </c>
       <c r="H181" t="n">
-        <v>-21</v>
+        <v>0.02</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>2855.1</v>
+        <v>2.79</v>
       </c>
       <c r="K181" t="n">
-        <v>2862.5</v>
+        <v>2.84</v>
       </c>
       <c r="L181" t="n">
-        <v>2879.5</v>
+        <v>2.86</v>
       </c>
       <c r="M181" t="n">
-        <v>2896.5</v>
+        <v>2.89</v>
       </c>
       <c r="N181" t="n">
-        <v>2908.7</v>
+        <v>2.93</v>
       </c>
       <c r="O181" t="n">
-        <v>2920.9</v>
+        <v>2.97</v>
       </c>
       <c r="P181" t="n">
-        <v>2942.7</v>
-      </c>
-      <c r="Q181" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
+        <v>2.97</v>
+      </c>
+      <c r="Q181" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="R181" t="inlineStr"/>
@@ -70722,61 +70722,61 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>白銀</t>
+          <t>Nasdaq 100 期貨</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>63.03</v>
+        <v>29200</v>
       </c>
       <c r="E182" t="n">
-        <v>63.64</v>
+        <v>29200</v>
       </c>
       <c r="F182" t="n">
-        <v>63.03</v>
+        <v>28918.75</v>
       </c>
       <c r="G182" t="n">
-        <v>63.24</v>
+        <v>28955</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.28</v>
+        <v>-197.25</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0068</v>
       </c>
       <c r="J182" t="n">
-        <v>62.34</v>
+        <v>28329.5</v>
       </c>
       <c r="K182" t="n">
-        <v>62.91</v>
+        <v>28711.81</v>
       </c>
       <c r="L182" t="n">
-        <v>63.17</v>
+        <v>28908.88</v>
       </c>
       <c r="M182" t="n">
-        <v>63.44</v>
+        <v>29105.94</v>
       </c>
       <c r="N182" t="n">
-        <v>63.85</v>
+        <v>29395.62</v>
       </c>
       <c r="O182" t="n">
-        <v>64.27</v>
+        <v>29685.31</v>
       </c>
       <c r="P182" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="Q182" s="6" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>29789.75</v>
+      </c>
+      <c r="Q182" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -70788,52 +70788,52 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SSE</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>上證綜合</t>
+          <t>Russell 2000 期貨</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3879.73</v>
+        <v>2896.4</v>
       </c>
       <c r="E183" t="n">
-        <v>3891.62</v>
+        <v>2896.5</v>
       </c>
       <c r="F183" t="n">
-        <v>3858.15</v>
+        <v>2862.7</v>
       </c>
       <c r="G183" t="n">
-        <v>3864.28</v>
+        <v>2873.1</v>
       </c>
       <c r="H183" t="n">
-        <v>-21.05</v>
+        <v>-21</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0073</v>
       </c>
       <c r="J183" t="n">
-        <v>3838.53</v>
+        <v>2855.1</v>
       </c>
       <c r="K183" t="n">
-        <v>3858.88</v>
+        <v>2862.5</v>
       </c>
       <c r="L183" t="n">
-        <v>3871.09</v>
+        <v>2879.5</v>
       </c>
       <c r="M183" t="n">
-        <v>3883.3</v>
+        <v>2896.5</v>
       </c>
       <c r="N183" t="n">
-        <v>3899.58</v>
+        <v>2908.7</v>
       </c>
       <c r="O183" t="n">
-        <v>3915.86</v>
+        <v>2920.9</v>
       </c>
       <c r="P183" t="n">
-        <v>3924</v>
+        <v>2942.7</v>
       </c>
       <c r="Q183" s="7" t="inlineStr">
         <is>
@@ -70850,61 +70850,61 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>白銀</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>45777</v>
+        <v>63.03</v>
       </c>
       <c r="E184" t="n">
-        <v>45964</v>
+        <v>63.64</v>
       </c>
       <c r="F184" t="n">
-        <v>45361</v>
+        <v>63.03</v>
       </c>
       <c r="G184" t="n">
-        <v>45556</v>
+        <v>63.24</v>
       </c>
       <c r="H184" t="n">
-        <v>-1032</v>
+        <v>-0.28</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>-0.0222</v>
+        <v>-0.0044</v>
       </c>
       <c r="J184" t="n">
-        <v>43941</v>
+        <v>62.34</v>
       </c>
       <c r="K184" t="n">
-        <v>45529.75</v>
+        <v>62.91</v>
       </c>
       <c r="L184" t="n">
-        <v>45907.5</v>
+        <v>63.17</v>
       </c>
       <c r="M184" t="n">
-        <v>46285.25</v>
+        <v>63.44</v>
       </c>
       <c r="N184" t="n">
-        <v>47268.5</v>
+        <v>63.85</v>
       </c>
       <c r="O184" t="n">
-        <v>48251.75</v>
+        <v>64.27</v>
       </c>
       <c r="P184" t="n">
-        <v>48024</v>
-      </c>
-      <c r="Q184" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
+        <v>64.38</v>
+      </c>
+      <c r="Q184" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -70916,63 +70916,59 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>USDTWD</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>美元對新台幣</t>
+          <t>上證綜合</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>31.72</v>
+        <v>3879.73</v>
       </c>
       <c r="E185" t="n">
-        <v>31.91</v>
+        <v>3891.62</v>
       </c>
       <c r="F185" t="n">
-        <v>31.69</v>
+        <v>3858.15</v>
       </c>
       <c r="G185" t="n">
-        <v>31.72</v>
+        <v>3864.28</v>
       </c>
       <c r="H185" t="n">
-        <v>0.04</v>
+        <v>-21.05</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0054</v>
       </c>
       <c r="J185" t="n">
-        <v>31.35</v>
+        <v>3838.53</v>
       </c>
       <c r="K185" t="n">
-        <v>31.38</v>
+        <v>3858.88</v>
       </c>
       <c r="L185" t="n">
-        <v>31.55</v>
+        <v>3871.09</v>
       </c>
       <c r="M185" t="n">
-        <v>31.71</v>
+        <v>3883.3</v>
       </c>
       <c r="N185" t="n">
-        <v>31.81</v>
+        <v>3899.58</v>
       </c>
       <c r="O185" t="n">
-        <v>31.9</v>
+        <v>3915.86</v>
       </c>
       <c r="P185" t="n">
-        <v>32.13</v>
+        <v>3924</v>
       </c>
       <c r="Q185" s="7" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -70982,250 +70978,254 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YM</t>
+          <t>T5F</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>道瓊期貨</t>
+          <t>台灣50期貨</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>52499</v>
+        <v>106.4</v>
       </c>
       <c r="E186" t="n">
-        <v>52499</v>
+        <v>107.15</v>
       </c>
       <c r="F186" t="n">
-        <v>51908</v>
+        <v>105.95</v>
       </c>
       <c r="G186" t="n">
-        <v>52115</v>
+        <v>106.2</v>
       </c>
       <c r="H186" t="n">
-        <v>-325</v>
+        <v>-2.45</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0225</v>
       </c>
       <c r="J186" t="n">
-        <v>51780</v>
+        <v>102.95</v>
       </c>
       <c r="K186" t="n">
-        <v>51989.5</v>
+        <v>106.42</v>
       </c>
       <c r="L186" t="n">
-        <v>52217</v>
+        <v>107.2</v>
       </c>
       <c r="M186" t="n">
-        <v>52444.5</v>
+        <v>107.97</v>
       </c>
       <c r="N186" t="n">
-        <v>52663</v>
+        <v>110.1</v>
       </c>
       <c r="O186" t="n">
-        <v>52881.5</v>
+        <v>112.22</v>
       </c>
       <c r="P186" t="n">
-        <v>53118</v>
+        <v>111.65</v>
       </c>
       <c r="Q186" s="7" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="R186" t="inlineStr"/>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>比特幣</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>75586.50999999999</v>
+        <v>45777</v>
       </c>
       <c r="E187" t="n">
-        <v>76003.17999999999</v>
+        <v>45964</v>
       </c>
       <c r="F187" t="n">
-        <v>75417.87</v>
+        <v>45361</v>
       </c>
       <c r="G187" t="n">
-        <v>75949.36</v>
+        <v>45556</v>
       </c>
       <c r="H187" t="n">
-        <v>-2214.02</v>
+        <v>-1032</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0222</v>
       </c>
       <c r="J187" t="n">
-        <v>73165.8</v>
+        <v>43941</v>
       </c>
       <c r="K187" t="n">
-        <v>75059.41</v>
+        <v>45529.75</v>
       </c>
       <c r="L187" t="n">
-        <v>76562.59</v>
+        <v>45907.5</v>
       </c>
       <c r="M187" t="n">
-        <v>78065.77</v>
+        <v>46285.25</v>
       </c>
       <c r="N187" t="n">
-        <v>79764.17</v>
+        <v>47268.5</v>
       </c>
       <c r="O187" t="n">
-        <v>81462.57000000001</v>
+        <v>48251.75</v>
       </c>
       <c r="P187" t="n">
-        <v>82770.53</v>
-      </c>
-      <c r="Q187" s="6" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>48024</v>
+      </c>
+      <c r="Q187" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>USDTWD</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>原油 WTI</t>
+          <t>美元對新台幣</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>105.48</v>
+        <v>31.72</v>
       </c>
       <c r="E188" t="n">
-        <v>105.63</v>
+        <v>31.91</v>
       </c>
       <c r="F188" t="n">
-        <v>104.23</v>
+        <v>31.69</v>
       </c>
       <c r="G188" t="n">
-        <v>104.82</v>
+        <v>31.72</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.01</v>
+        <v>0.04</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0013</v>
       </c>
       <c r="J188" t="n">
-        <v>95.67</v>
+        <v>31.35</v>
       </c>
       <c r="K188" t="n">
-        <v>101.22</v>
+        <v>31.38</v>
       </c>
       <c r="L188" t="n">
-        <v>103.06</v>
+        <v>31.55</v>
       </c>
       <c r="M188" t="n">
-        <v>104.91</v>
+        <v>31.71</v>
       </c>
       <c r="N188" t="n">
-        <v>108.6</v>
+        <v>31.81</v>
       </c>
       <c r="O188" t="n">
-        <v>112.3</v>
+        <v>31.9</v>
       </c>
       <c r="P188" t="n">
-        <v>112.29</v>
-      </c>
-      <c r="Q188" s="6" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>32.13</v>
+      </c>
+      <c r="Q188" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>YM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>S&amp;P 500 期貨</t>
+          <t>道瓊期貨</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>7663.25</v>
+        <v>52499</v>
       </c>
       <c r="E189" t="n">
-        <v>7678</v>
+        <v>52499</v>
       </c>
       <c r="F189" t="n">
-        <v>7658.75</v>
+        <v>51908</v>
       </c>
       <c r="G189" t="n">
-        <v>7670.5</v>
+        <v>52115</v>
       </c>
       <c r="H189" t="n">
-        <v>81.25</v>
+        <v>-325</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0062</v>
       </c>
       <c r="J189" t="n">
-        <v>7520.25</v>
+        <v>51780</v>
       </c>
       <c r="K189" t="n">
-        <v>7524.88</v>
+        <v>51989.5</v>
       </c>
       <c r="L189" t="n">
-        <v>7561</v>
+        <v>52217</v>
       </c>
       <c r="M189" t="n">
-        <v>7597.12</v>
+        <v>52444.5</v>
       </c>
       <c r="N189" t="n">
-        <v>7617.5</v>
+        <v>52663</v>
       </c>
       <c r="O189" t="n">
-        <v>7637.88</v>
+        <v>52881.5</v>
       </c>
       <c r="P189" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="Q189" s="6" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>53118</v>
+      </c>
+      <c r="Q189" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="R189" t="inlineStr"/>
@@ -71238,59 +71238,63 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>以太幣</t>
+          <t>比特幣</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2397.64</v>
+        <v>75586.50999999999</v>
       </c>
       <c r="E190" t="n">
-        <v>2408.58</v>
+        <v>76009.16</v>
       </c>
       <c r="F190" t="n">
-        <v>2389.89</v>
+        <v>75349.47</v>
       </c>
       <c r="G190" t="n">
-        <v>2405.93</v>
+        <v>75941.33</v>
       </c>
       <c r="H190" t="n">
-        <v>-108.48</v>
+        <v>328.82</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>-0.0431</v>
+        <v>0.0043</v>
       </c>
       <c r="J190" t="n">
-        <v>2318.45</v>
+        <v>71646.64</v>
       </c>
       <c r="K190" t="n">
-        <v>2355.18</v>
+        <v>71824.02</v>
       </c>
       <c r="L190" t="n">
-        <v>2440.92</v>
+        <v>73963.53</v>
       </c>
       <c r="M190" t="n">
-        <v>2526.66</v>
+        <v>76103.03999999999</v>
       </c>
       <c r="N190" t="n">
-        <v>2587.9</v>
+        <v>77261.48</v>
       </c>
       <c r="O190" t="n">
-        <v>2649.13</v>
+        <v>78419.92999999999</v>
       </c>
       <c r="P190" t="n">
-        <v>2759.38</v>
-      </c>
-      <c r="Q190" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr"/>
+        <v>81540.5</v>
+      </c>
+      <c r="Q190" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -71300,61 +71304,61 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>黃金</t>
+          <t>原油 WTI</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4333.5</v>
+        <v>105.48</v>
       </c>
       <c r="E191" t="n">
-        <v>4381.9</v>
+        <v>105.63</v>
       </c>
       <c r="F191" t="n">
-        <v>4315.2</v>
+        <v>102.85</v>
       </c>
       <c r="G191" t="n">
-        <v>4371</v>
+        <v>103.27</v>
       </c>
       <c r="H191" t="n">
-        <v>38.2</v>
+        <v>-2.56</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0242</v>
       </c>
       <c r="J191" t="n">
-        <v>4245</v>
+        <v>95.67</v>
       </c>
       <c r="K191" t="n">
-        <v>4277.65</v>
+        <v>101.22</v>
       </c>
       <c r="L191" t="n">
-        <v>4304.5</v>
+        <v>103.06</v>
       </c>
       <c r="M191" t="n">
-        <v>4331.35</v>
+        <v>104.91</v>
       </c>
       <c r="N191" t="n">
-        <v>4361.1</v>
+        <v>108.6</v>
       </c>
       <c r="O191" t="n">
-        <v>4390.85</v>
+        <v>112.3</v>
       </c>
       <c r="P191" t="n">
-        <v>4414.8</v>
-      </c>
-      <c r="Q191" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
+        <v>112.29</v>
+      </c>
+      <c r="Q191" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -71366,63 +71370,59 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>天然氣</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2.94</v>
+        <v>25515.96</v>
       </c>
       <c r="E192" t="n">
-        <v>2.95</v>
+        <v>25524.04</v>
       </c>
       <c r="F192" t="n">
-        <v>2.92</v>
+        <v>25361.7</v>
       </c>
       <c r="G192" t="n">
-        <v>2.92</v>
+        <v>25492</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>89.72</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0035</v>
       </c>
       <c r="J192" t="n">
-        <v>2.79</v>
+        <v>24866.8</v>
       </c>
       <c r="K192" t="n">
-        <v>2.84</v>
+        <v>25134.36</v>
       </c>
       <c r="L192" t="n">
-        <v>2.88</v>
+        <v>25249.23</v>
       </c>
       <c r="M192" t="n">
-        <v>2.91</v>
+        <v>25364.11</v>
       </c>
       <c r="N192" t="n">
-        <v>2.96</v>
+        <v>25555.32</v>
       </c>
       <c r="O192" t="n">
-        <v>3</v>
+        <v>25746.54</v>
       </c>
       <c r="P192" t="n">
-        <v>3.03</v>
+        <v>25785.07</v>
       </c>
       <c r="Q192" s="6" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -71432,52 +71432,52 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nasdaq 100 期貨</t>
+          <t>S&amp;P 500 期貨</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>29263.75</v>
+        <v>7663.25</v>
       </c>
       <c r="E193" t="n">
-        <v>29358.5</v>
+        <v>7681.5</v>
       </c>
       <c r="F193" t="n">
-        <v>29226</v>
+        <v>7658.75</v>
       </c>
       <c r="G193" t="n">
-        <v>29323.5</v>
+        <v>7675.75</v>
       </c>
       <c r="H193" t="n">
-        <v>368.5</v>
+        <v>86.5</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>0.0127</v>
+        <v>0.0114</v>
       </c>
       <c r="J193" t="n">
-        <v>28637.5</v>
+        <v>7520.25</v>
       </c>
       <c r="K193" t="n">
-        <v>28621.56</v>
+        <v>7524.88</v>
       </c>
       <c r="L193" t="n">
-        <v>28814.38</v>
+        <v>7561</v>
       </c>
       <c r="M193" t="n">
-        <v>29007.19</v>
+        <v>7597.12</v>
       </c>
       <c r="N193" t="n">
-        <v>29095.62</v>
+        <v>7617.5</v>
       </c>
       <c r="O193" t="n">
-        <v>29184.06</v>
+        <v>7637.88</v>
       </c>
       <c r="P193" t="n">
-        <v>29481.25</v>
+        <v>7689.75</v>
       </c>
       <c r="Q193" s="6" t="inlineStr">
         <is>
@@ -71494,52 +71494,52 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Russell 2000 期貨</t>
+          <t>以太幣</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2898.5</v>
+        <v>2397.64</v>
       </c>
       <c r="E194" t="n">
-        <v>2903.3</v>
+        <v>2411.55</v>
       </c>
       <c r="F194" t="n">
-        <v>2894.8</v>
+        <v>2385.07</v>
       </c>
       <c r="G194" t="n">
-        <v>2898.9</v>
+        <v>2411.88</v>
       </c>
       <c r="H194" t="n">
-        <v>25.8</v>
+        <v>12.79</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="J194" t="n">
-        <v>2828.9</v>
+        <v>2196.6</v>
       </c>
       <c r="K194" t="n">
-        <v>2836.05</v>
+        <v>2217.95</v>
       </c>
       <c r="L194" t="n">
-        <v>2856.2</v>
+        <v>2318.41</v>
       </c>
       <c r="M194" t="n">
-        <v>2876.35</v>
+        <v>2418.86</v>
       </c>
       <c r="N194" t="n">
-        <v>2890</v>
+        <v>2479.77</v>
       </c>
       <c r="O194" t="n">
-        <v>2903.65</v>
+        <v>2540.67</v>
       </c>
       <c r="P194" t="n">
-        <v>2930.3</v>
+        <v>2680.68</v>
       </c>
       <c r="Q194" s="7" t="inlineStr">
         <is>
@@ -71548,7 +71548,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -71560,59 +71560,63 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FTSE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>白銀</t>
+          <t>FTSE 100</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>64.18000000000001</v>
+        <v>10658.22</v>
       </c>
       <c r="E195" t="n">
-        <v>65.39</v>
+        <v>10731.31</v>
       </c>
       <c r="F195" t="n">
-        <v>63.94</v>
+        <v>10655.82</v>
       </c>
       <c r="G195" t="n">
-        <v>65.20999999999999</v>
+        <v>10722.09</v>
       </c>
       <c r="H195" t="n">
-        <v>1.98</v>
+        <v>63.99</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>0.0313</v>
+        <v>0.006</v>
       </c>
       <c r="J195" t="n">
-        <v>62.42</v>
+        <v>10475</v>
       </c>
       <c r="K195" t="n">
-        <v>62.58</v>
+        <v>10554.7</v>
       </c>
       <c r="L195" t="n">
-        <v>62.93</v>
+        <v>10602.4</v>
       </c>
       <c r="M195" t="n">
-        <v>63.29</v>
+        <v>10650.1</v>
       </c>
       <c r="N195" t="n">
-        <v>63.54</v>
+        <v>10713.8</v>
       </c>
       <c r="O195" t="n">
-        <v>63.8</v>
+        <v>10777.5</v>
       </c>
       <c r="P195" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="Q195" s="6" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr"/>
+        <v>10809.2</v>
+      </c>
+      <c r="Q195" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -71622,59 +71626,63 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>黃金</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>45533</v>
+        <v>4333.5</v>
       </c>
       <c r="E196" t="n">
-        <v>45736</v>
+        <v>4394.5</v>
       </c>
       <c r="F196" t="n">
-        <v>45330</v>
+        <v>4315.2</v>
       </c>
       <c r="G196" t="n">
-        <v>45529</v>
+        <v>4389.8</v>
       </c>
       <c r="H196" t="n">
-        <v>-27</v>
+        <v>57</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0132</v>
       </c>
       <c r="J196" t="n">
-        <v>44758</v>
+        <v>4245</v>
       </c>
       <c r="K196" t="n">
-        <v>44899.75</v>
+        <v>4277.65</v>
       </c>
       <c r="L196" t="n">
-        <v>45254.5</v>
+        <v>4304.5</v>
       </c>
       <c r="M196" t="n">
-        <v>45609.25</v>
+        <v>4331.35</v>
       </c>
       <c r="N196" t="n">
-        <v>45857.5</v>
+        <v>4361.1</v>
       </c>
       <c r="O196" t="n">
-        <v>46105.75</v>
+        <v>4390.85</v>
       </c>
       <c r="P196" t="n">
-        <v>46567</v>
+        <v>4414.8</v>
       </c>
       <c r="Q196" s="7" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="R196" t="inlineStr"/>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -71684,52 +71692,52 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>USDTWD</t>
+          <t>HSI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>美元對新台幣</t>
+          <t>恆生指數</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>31.8</v>
+        <v>24789.91</v>
       </c>
       <c r="E197" t="n">
-        <v>31.92</v>
+        <v>24789.91</v>
       </c>
       <c r="F197" t="n">
-        <v>31.71</v>
+        <v>24574.75</v>
       </c>
       <c r="G197" t="n">
-        <v/>
+        <v>24713.78</v>
       </c>
       <c r="H197" t="n">
-        <v/>
+        <v>46.54</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v/>
+        <v>0.0019</v>
       </c>
       <c r="J197" t="n">
-        <v>31.47</v>
+        <v>24379.96</v>
       </c>
       <c r="K197" t="n">
-        <v>31.46</v>
+        <v>24326.04</v>
       </c>
       <c r="L197" t="n">
-        <v>31.61</v>
+        <v>24528.71</v>
       </c>
       <c r="M197" t="n">
-        <v>31.76</v>
+        <v>24731.39</v>
       </c>
       <c r="N197" t="n">
-        <v>31.83</v>
+        <v>24805.77</v>
       </c>
       <c r="O197" t="n">
-        <v>31.89</v>
+        <v>24880.14</v>
       </c>
       <c r="P197" t="n">
-        <v>32.13</v>
+        <v>25211.11</v>
       </c>
       <c r="Q197" s="7" t="inlineStr">
         <is>
@@ -71738,7 +71746,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -71750,59 +71758,645 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
+          <t>N225</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>日經 225</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>63672.13</v>
+      </c>
+      <c r="E198" t="n">
+        <v>63923</v>
+      </c>
+      <c r="F198" t="n">
+        <v>63209.92</v>
+      </c>
+      <c r="G198" t="n">
+        <v>63923</v>
+      </c>
+      <c r="H198" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="J198" t="n">
+        <v>62033.36</v>
+      </c>
+      <c r="K198" t="n">
+        <v>62400.29</v>
+      </c>
+      <c r="L198" t="n">
+        <v>62967.19</v>
+      </c>
+      <c r="M198" t="n">
+        <v>63534.1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>64001.01</v>
+      </c>
+      <c r="O198" t="n">
+        <v>64467.93</v>
+      </c>
+      <c r="P198" t="n">
+        <v>65134.82</v>
+      </c>
+      <c r="Q198" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>天然氣</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G199" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="J199" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K199" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L199" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M199" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O199" t="n">
+        <v>3</v>
+      </c>
+      <c r="P199" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q199" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Nasdaq 100 期貨</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>29263.75</v>
+      </c>
+      <c r="E200" t="n">
+        <v>29419.25</v>
+      </c>
+      <c r="F200" t="n">
+        <v>29226</v>
+      </c>
+      <c r="G200" t="n">
+        <v>29382</v>
+      </c>
+      <c r="H200" t="n">
+        <v>427</v>
+      </c>
+      <c r="I200" s="5" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="J200" t="n">
+        <v>28637.5</v>
+      </c>
+      <c r="K200" t="n">
+        <v>28621.56</v>
+      </c>
+      <c r="L200" t="n">
+        <v>28814.38</v>
+      </c>
+      <c r="M200" t="n">
+        <v>29007.19</v>
+      </c>
+      <c r="N200" t="n">
+        <v>29095.62</v>
+      </c>
+      <c r="O200" t="n">
+        <v>29184.06</v>
+      </c>
+      <c r="P200" t="n">
+        <v>29481.25</v>
+      </c>
+      <c r="Q200" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Russell 2000 期貨</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2898.5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2903.6</v>
+      </c>
+      <c r="F201" t="n">
+        <v>2892.5</v>
+      </c>
+      <c r="G201" t="n">
+        <v>2900.4</v>
+      </c>
+      <c r="H201" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="J201" t="n">
+        <v>2828.9</v>
+      </c>
+      <c r="K201" t="n">
+        <v>2836.05</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2856.2</v>
+      </c>
+      <c r="M201" t="n">
+        <v>2876.35</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2890</v>
+      </c>
+      <c r="O201" t="n">
+        <v>2903.65</v>
+      </c>
+      <c r="P201" t="n">
+        <v>2930.3</v>
+      </c>
+      <c r="Q201" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>白銀</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="E202" t="n">
+        <v>65.42</v>
+      </c>
+      <c r="F202" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="G202" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="J202" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="K202" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="L202" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="M202" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="N202" t="n">
+        <v>63.54</v>
+      </c>
+      <c r="O202" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="P202" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="Q202" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SSE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>上證綜合</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>3861.75</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3894.66</v>
+      </c>
+      <c r="F203" t="n">
+        <v>3842.72</v>
+      </c>
+      <c r="G203" t="n">
+        <v>3891.6</v>
+      </c>
+      <c r="H203" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3824.68</v>
+      </c>
+      <c r="K203" t="n">
+        <v>3825.51</v>
+      </c>
+      <c r="L203" t="n">
+        <v>3847.54</v>
+      </c>
+      <c r="M203" t="n">
+        <v>3869.58</v>
+      </c>
+      <c r="N203" t="n">
+        <v>3881.01</v>
+      </c>
+      <c r="O203" t="n">
+        <v>3892.45</v>
+      </c>
+      <c r="P203" t="n">
+        <v>3925.09</v>
+      </c>
+      <c r="Q203" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>T5F</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>台灣50期貨</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="E204" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="F204" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="G204" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="J204" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="K204" t="n">
+        <v>104.82</v>
+      </c>
+      <c r="L204" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="M204" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="N204" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="O204" t="n">
+        <v>107.22</v>
+      </c>
+      <c r="P204" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="Q204" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>台指期</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>45534</v>
+      </c>
+      <c r="E205" t="n">
+        <v>46093</v>
+      </c>
+      <c r="F205" t="n">
+        <v>45330</v>
+      </c>
+      <c r="G205" t="n">
+        <v>45529</v>
+      </c>
+      <c r="H205" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="J205" t="n">
+        <v>44758</v>
+      </c>
+      <c r="K205" t="n">
+        <v>44899.75</v>
+      </c>
+      <c r="L205" t="n">
+        <v>45254.5</v>
+      </c>
+      <c r="M205" t="n">
+        <v>45609.25</v>
+      </c>
+      <c r="N205" t="n">
+        <v>45857.5</v>
+      </c>
+      <c r="O205" t="n">
+        <v>46105.75</v>
+      </c>
+      <c r="P205" t="n">
+        <v>46567</v>
+      </c>
+      <c r="Q205" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>USDTWD</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>美元對新台幣</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E206" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="F206" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="G206" t="n">
+        <v/>
+      </c>
+      <c r="H206" t="n">
+        <v/>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J206" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="K206" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="L206" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="M206" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="N206" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="O206" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="P206" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="Q206" s="7" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
           <t>YM</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>道瓊期貨</t>
         </is>
       </c>
-      <c r="D198" t="n">
+      <c r="D207" t="n">
         <v>52576</v>
       </c>
-      <c r="E198" t="n">
-        <v>52678</v>
-      </c>
-      <c r="F198" t="n">
-        <v>52557</v>
-      </c>
-      <c r="G198" t="n">
-        <v>52617</v>
-      </c>
-      <c r="H198" t="n">
-        <v>502</v>
-      </c>
-      <c r="I198" s="5" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="J198" t="n">
+      <c r="E207" t="n">
+        <v>52687</v>
+      </c>
+      <c r="F207" t="n">
+        <v>52524</v>
+      </c>
+      <c r="G207" t="n">
+        <v>52644</v>
+      </c>
+      <c r="H207" t="n">
+        <v>529</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="J207" t="n">
         <v>51317</v>
       </c>
-      <c r="K198" t="n">
+      <c r="K207" t="n">
         <v>51479.75</v>
       </c>
-      <c r="L198" t="n">
+      <c r="L207" t="n">
         <v>51819.5</v>
       </c>
-      <c r="M198" t="n">
+      <c r="M207" t="n">
         <v>52159.25</v>
       </c>
-      <c r="N198" t="n">
+      <c r="N207" t="n">
         <v>52410.5</v>
       </c>
-      <c r="O198" t="n">
+      <c r="O207" t="n">
         <v>52661.75</v>
       </c>
-      <c r="P198" t="n">
+      <c r="P207" t="n">
         <v>53090</v>
       </c>
-      <c r="Q198" s="7" t="inlineStr">
+      <c r="Q207" s="7" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="R198" t="inlineStr">
+      <c r="R207" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/reports/monthly_report.xlsx
+++ b/three_gate/reports/monthly_report.xlsx
@@ -71250,19 +71250,19 @@
         <v>75586.50999999999</v>
       </c>
       <c r="E190" t="n">
-        <v>76009.16</v>
+        <v>76185.77</v>
       </c>
       <c r="F190" t="n">
         <v>75349.47</v>
       </c>
       <c r="G190" t="n">
-        <v>75941.33</v>
+        <v>76176.73</v>
       </c>
       <c r="H190" t="n">
-        <v>328.82</v>
+        <v>564.22</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0075</v>
       </c>
       <c r="J190" t="n">
         <v>71646.64</v>
@@ -71322,13 +71322,13 @@
         <v>102.85</v>
       </c>
       <c r="G191" t="n">
-        <v>103.27</v>
+        <v>103.22</v>
       </c>
       <c r="H191" t="n">
-        <v>-2.56</v>
+        <v>-2.61</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0247</v>
       </c>
       <c r="J191" t="n">
         <v>95.67</v>
@@ -71388,13 +71388,13 @@
         <v>25361.7</v>
       </c>
       <c r="G192" t="n">
-        <v>25492</v>
+        <v>25499.35</v>
       </c>
       <c r="H192" t="n">
-        <v>89.72</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="J192" t="n">
         <v>24866.8</v>
@@ -71444,19 +71444,19 @@
         <v>7663.25</v>
       </c>
       <c r="E193" t="n">
-        <v>7681.5</v>
+        <v>7683.5</v>
       </c>
       <c r="F193" t="n">
         <v>7658.75</v>
       </c>
       <c r="G193" t="n">
-        <v>7675.75</v>
+        <v>7683.25</v>
       </c>
       <c r="H193" t="n">
-        <v>86.5</v>
+        <v>94</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>0.0114</v>
+        <v>0.0124</v>
       </c>
       <c r="J193" t="n">
         <v>7520.25</v>
@@ -71506,19 +71506,19 @@
         <v>2397.64</v>
       </c>
       <c r="E194" t="n">
-        <v>2411.55</v>
+        <v>2424.1</v>
       </c>
       <c r="F194" t="n">
         <v>2385.07</v>
       </c>
       <c r="G194" t="n">
-        <v>2411.88</v>
+        <v>2417.66</v>
       </c>
       <c r="H194" t="n">
-        <v>12.79</v>
+        <v>18.57</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0077</v>
       </c>
       <c r="J194" t="n">
         <v>2196.6</v>
@@ -71572,19 +71572,19 @@
         <v>10658.22</v>
       </c>
       <c r="E195" t="n">
-        <v>10731.31</v>
+        <v>10732.15</v>
       </c>
       <c r="F195" t="n">
         <v>10655.82</v>
       </c>
       <c r="G195" t="n">
-        <v>10722.09</v>
+        <v>10731.97</v>
       </c>
       <c r="H195" t="n">
-        <v>63.99</v>
+        <v>73.87</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0069</v>
       </c>
       <c r="J195" t="n">
         <v>10475</v>
@@ -71638,19 +71638,19 @@
         <v>4333.5</v>
       </c>
       <c r="E196" t="n">
-        <v>4394.5</v>
+        <v>4394.8</v>
       </c>
       <c r="F196" t="n">
         <v>4315.2</v>
       </c>
       <c r="G196" t="n">
-        <v>4389.8</v>
+        <v>4384.9</v>
       </c>
       <c r="H196" t="n">
-        <v>57</v>
+        <v>52.1</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>0.0132</v>
+        <v>0.012</v>
       </c>
       <c r="J196" t="n">
         <v>4245</v>
@@ -71842,13 +71842,13 @@
         <v>2.9</v>
       </c>
       <c r="G199" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="H199" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0075</v>
       </c>
       <c r="J199" t="n">
         <v>2.79</v>
@@ -71908,13 +71908,13 @@
         <v>29226</v>
       </c>
       <c r="G200" t="n">
-        <v>29382</v>
+        <v>29413.25</v>
       </c>
       <c r="H200" t="n">
-        <v>427</v>
+        <v>458.25</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0158</v>
       </c>
       <c r="J200" t="n">
         <v>28637.5</v>
@@ -71964,19 +71964,19 @@
         <v>2898.5</v>
       </c>
       <c r="E201" t="n">
-        <v>2903.6</v>
+        <v>2904.7</v>
       </c>
       <c r="F201" t="n">
         <v>2892.5</v>
       </c>
       <c r="G201" t="n">
-        <v>2900.4</v>
+        <v>2903.8</v>
       </c>
       <c r="H201" t="n">
-        <v>27.3</v>
+        <v>30.7</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0107</v>
       </c>
       <c r="J201" t="n">
         <v>2828.9</v>
@@ -71999,16 +71999,12 @@
       <c r="P201" t="n">
         <v>2930.3</v>
       </c>
-      <c r="Q201" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="Q201" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -72030,19 +72026,19 @@
         <v>64.18000000000001</v>
       </c>
       <c r="E202" t="n">
-        <v>65.42</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F202" t="n">
         <v>63.94</v>
       </c>
       <c r="G202" t="n">
-        <v>65.36</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="H202" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="J202" t="n">
         <v>62.42</v>
@@ -72356,19 +72352,19 @@
         <v>52576</v>
       </c>
       <c r="E207" t="n">
-        <v>52687</v>
+        <v>52697</v>
       </c>
       <c r="F207" t="n">
         <v>52524</v>
       </c>
       <c r="G207" t="n">
-        <v>52644</v>
+        <v>52695</v>
       </c>
       <c r="H207" t="n">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0111</v>
       </c>
       <c r="J207" t="n">
         <v>51317</v>
@@ -72391,16 +72387,12 @@
       <c r="P207" t="n">
         <v>53090</v>
       </c>
-      <c r="Q207" s="7" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="Q207" s="6" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
